--- a/data/trans_bre/IP07_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R2-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,41</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-5,86%</t>
+          <t>-13,66%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 2,77</t>
+          <t>-3,26; 2,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 5,18</t>
+          <t>-0,82; 5,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 4,04</t>
+          <t>-2,47; 4,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 3,95</t>
+          <t>-4,22; 3,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-76,27; 242,4</t>
+          <t>-81,99; 235,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-72,83; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-87,65; 424,59</t>
+          <t>-78,89; 604,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-86,8; 437,98</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,77</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>178,05%</t>
+          <t>65,33%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,05; -0,6</t>
+          <t>-6,43; -0,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,83</t>
+          <t>-2,0; 1,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 2,31</t>
+          <t>-1,95; 2,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 14,82</t>
+          <t>-1,42; 4,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-84,76; -7,06</t>
+          <t>-85,4; -7,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,86; 437,13</t>
+          <t>-85,02; 444,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,43; 253,72</t>
+          <t>-70,73; 268,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 1336,82</t>
+          <t>-63,68; 376,6</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>1,41</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,96</t>
+          <t>-3,05; 2,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 2,64</t>
+          <t>-3,85; 2,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 1,39</t>
+          <t>-4,05; 1,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,44</t>
+          <t>-1,36; 4,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-95,23; 251,88</t>
+          <t>-88,77; 322,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-71,71; 135,28</t>
+          <t>-72,86; 92,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-85,64; 103,0</t>
+          <t>-85,25; 120,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-76,69; 838,86</t>
+          <t>-76,88; 1280,3</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-60,2%</t>
+          <t>-60,61%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,48; -0,26</t>
+          <t>-4,49; -0,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 1,7</t>
+          <t>-3,69; 1,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,53</t>
+          <t>-2,09; 1,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 0,48</t>
+          <t>-5,23; 0,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 56,01</t>
+          <t>-100,0; 31,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,79; 106,9</t>
+          <t>-75,67; 118,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 444,12</t>
+          <t>-100,0; 683,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 72,84</t>
+          <t>-100,0; 67,7</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,14; -0,52</t>
+          <t>-3,3; -0,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,2</t>
+          <t>-1,45; 1,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,07</t>
+          <t>-1,38; 1,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,91</t>
+          <t>-1,53; 1,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-72,74; -13,8</t>
+          <t>-74,28; -14,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,71; 64,05</t>
+          <t>-47,45; 72,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-50,0; 74,47</t>
+          <t>-51,57; 70,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-32,22; 182,94</t>
+          <t>-46,82; 92,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP07_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R2-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,191 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,76</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,41</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-7,89%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>130,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>35,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-13,66%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.2069184001658859</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.676238321304589</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.7565361693981569</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.4144924281851585</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.07890450293027881</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1.306795152987316</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.3546116896130548</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.1366487114634362</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,26; 2,71</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-0,82; 5,16</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,47; 4,19</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-4,22; 3,47</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-81,99; 235,64</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-78,89; 604,27</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.260047320251933</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.8202814339064314</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.46625107876124</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-4.21549964985658</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.819864294020463</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="n">
+        <v>-0.7888833686390827</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.705812020147048</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5.162272075040588</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.192745933489118</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3.466404402997162</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.356443233037411</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="n">
+        <v>6.042683586599675</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-3,49</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,21</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-60,57%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-12,21%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,53%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>65,33%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-6,43; -0,78</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,0; 1,69</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,95; 2,2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-1,42; 4,3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-85,4; -7,21</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-85,02; 444,39</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-70,73; 268,91</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-63,68; 376,6</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-3.488078085758739</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.1796156130241175</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.2144846500888982</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.296578672784119</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.6056518603181041</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1220753481949034</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.1152637237000347</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.653305423065755</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,48</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,22</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,41</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-21,72%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-18,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-37,62%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>94,15%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-6.432594556905976</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.002634692913383</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.945423417642657</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-1.422618580209113</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.8540423079049757</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8502372179045947</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.7072940408820574</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6368032694766025</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,05; 2,08</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,85; 2,13</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,05; 1,53</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-1,36; 4,51</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-88,77; 322,1</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-72,86; 92,85</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-85,25; 120,5</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-76,88; 1280,3</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-0.784200634236042</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.685660196378554</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.197211417102506</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.297504318908591</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.07210040074308188</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>4.443909494371868</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>2.689055323089874</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>3.766024564838494</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +811,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-2,18</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,03</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,18</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-75,55%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-29,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-23,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-60,61%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.4806313487994082</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.7080118787440366</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.21680939440958</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.405309400888449</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2172116282531117</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1866185785585636</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.3761907336179008</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.9415115939458879</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,49; -0,37</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,69; 1,6</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,09; 1,45</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-5,23; 0,76</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 31,03</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-75,67; 118,71</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 683,58</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 67,7</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.045850402322564</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.852697058787587</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.054856784542981</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.356358249923267</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.8876621999789041</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.728607370306667</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.8525397937424363</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.7687563489429219</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.078688472693431</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.129354672773466</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.525150678915819</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.506980720510642</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>3.221045689048061</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.9284633086208938</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.205007657074448</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>12.80304750037086</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-2.176828376982874</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.034652244390769</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.3263895134934521</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.179806965303724</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.755520749556636</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2991357537763012</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.2376914608629815</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.6061233575957302</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.490200151577154</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.692375714496805</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.089823315732814</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-5.23422442614984</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.7567424142916106</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-0.3719080165426359</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.597919997219227</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.450356960758167</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.7593659164719559</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.3102621957258873</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.187114981884889</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>6.835814362114741</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.6770122293579193</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,82</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-51,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-6,16%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-8,33%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-3,3; -0,54</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,45; 1,22</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,38; 1,02</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,53; 1,54</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-74,28; -14,75</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-47,45; 72,13</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-51,57; 70,58</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-46,82; 92,64</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-1.82031952900089</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.1538265050976439</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.1740796697692185</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.1189184607911353</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.5156376531532615</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.06159639618925046</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.08334277861835468</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.04865030289343336</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.295542617938637</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.451244335341537</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.379536634705319</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.53279939678702</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.7427642703977334</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.474489175088241</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.5157241096654185</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.4682405516257258</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>-0.5445886347575007</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.223982574820716</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.021592243925387</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.540648846660291</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-0.1474772761140006</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.7213148389015263</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.7057769517258944</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.9263900943238097</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1109,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
